--- a/DataAnalysis/AdditionalModels/Discriminators/CJ/0.3/CLSDIV/res_scrimin=1.csv.xlsx
+++ b/DataAnalysis/AdditionalModels/Discriminators/CJ/0.3/CLSDIV/res_scrimin=1.csv.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\Discriminators\CI\0.3\CLSDIV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\AdditionalModels\Discriminators\CJ\0.3\CLSDIV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5BEFFB-0D3B-4106-8EB0-71AFE669C170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76879F88-621F-4FE4-BCA0-4A66B8A46605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F214021-6FB1-40D5-9709-F0BEE25B15FC}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="37">
   <si>
     <t>Procedo per riga (prima riga, poi seconda riga, …)</t>
   </si>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Rec2</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>Class 0</t>
+  </si>
+  <si>
+    <t>Class 1</t>
+  </si>
+  <si>
+    <t>Class 2</t>
+  </si>
+  <si>
+    <t>CM</t>
   </si>
 </sst>
 </file>
@@ -1005,10 +1020,18 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,36 +1130,64 @@
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>154</v>
+      </c>
+      <c r="D2" s="1">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1">
+        <v>22</v>
+      </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="G2" s="1">
+        <v>154</v>
+      </c>
+      <c r="H2" s="1">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1">
+        <v>159</v>
+      </c>
+      <c r="L2" s="1">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1">
+        <v>19</v>
+      </c>
+      <c r="N2" s="1">
+        <v>17</v>
+      </c>
+      <c r="O2" s="1">
+        <v>164</v>
+      </c>
       <c r="P2" s="1">
         <f>G2+K2+O2</f>
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="Q2" s="1">
         <f>G2+J2+M2</f>
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="R2" s="1">
         <f>H2+K2+N2</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S2" s="1">
         <f>I2+L2+O2</f>
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="T2" s="1">
         <v>200</v>
@@ -1147,29 +1198,29 @@
       <c r="V2" s="1">
         <v>200</v>
       </c>
-      <c r="W2" s="1" t="e">
+      <c r="W2" s="1">
         <f>G2/Q2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" s="1" t="e">
+        <v>0.79381443298969068</v>
+      </c>
+      <c r="X2" s="1">
         <f>K2/R2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" s="1" t="e">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="Y2" s="1">
         <f>O2/S2</f>
-        <v>#DIV/0!</v>
+        <v>0.79611650485436891</v>
       </c>
       <c r="Z2" s="1">
         <f>G2/T2</f>
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AA2" s="1">
         <f>K2/U2</f>
-        <v>0</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="AB2" s="1">
         <f>O2/V2</f>
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AC2" s="1">
         <f>SUM(T2:V2)</f>
@@ -1177,100 +1228,240 @@
       </c>
       <c r="AD2" s="1">
         <f>P2/AC2</f>
-        <v>0</v>
-      </c>
-      <c r="AF2" t="e">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="AF2">
         <f t="shared" ref="AF2:AK2" si="0">AVERAGE(W2:W10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2" t="e">
+        <v>0.80848738682573251</v>
+      </c>
+      <c r="AG2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH2" t="e">
+        <v>0.80334606186151125</v>
+      </c>
+      <c r="AH2">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.79514983417908602</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="AJ2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="AK2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="AL2">
         <f>AVERAGE(AD2:AD10)</f>
-        <v>0</v>
+        <v>0.80099999999999993</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1">
+        <v>159</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20</v>
+      </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
+      <c r="G3" s="1">
+        <v>155</v>
+      </c>
+      <c r="H3" s="1">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1">
+        <v>166</v>
+      </c>
+      <c r="L3" s="1">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1">
+        <v>17</v>
+      </c>
+      <c r="N3" s="1">
+        <v>21</v>
+      </c>
+      <c r="O3" s="1">
+        <v>162</v>
+      </c>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P6" si="1">G3+K3+O3</f>
+        <v>483</v>
+      </c>
+      <c r="Q3" s="1">
+        <f t="shared" ref="Q3:Q6" si="2">G3+J3+M3</f>
+        <v>188</v>
+      </c>
+      <c r="R3" s="1">
+        <f t="shared" ref="R3:R6" si="3">H3+K3+N3</f>
+        <v>214</v>
+      </c>
+      <c r="S3" s="1">
+        <f t="shared" ref="S3:S6" si="4">I3+L3+O3</f>
+        <v>198</v>
+      </c>
+      <c r="T3" s="1">
+        <v>200</v>
+      </c>
+      <c r="U3" s="1">
+        <v>200</v>
+      </c>
+      <c r="V3" s="1">
+        <v>200</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ref="W3:W6" si="5">G3/Q3</f>
+        <v>0.82446808510638303</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ref="X3:X6" si="6">K3/R3</f>
+        <v>0.77570093457943923</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ref="Y3:Y6" si="7">O3/S3</f>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ref="Z3:Z6" si="8">G3/T3</f>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ref="AA3:AA6" si="9">K3/U3</f>
+        <v>0.83</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ref="AB3:AB6" si="10">O3/V3</f>
+        <v>0.81</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ref="AC3:AC6" si="11">SUM(T3:V3)</f>
+        <v>600</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ref="AD3:AD6" si="12">P3/AC3</f>
+        <v>0.80500000000000005</v>
+      </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1">
+        <v>164</v>
+      </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+      <c r="G4" s="1">
+        <v>153</v>
+      </c>
+      <c r="H4" s="1">
+        <v>29</v>
+      </c>
+      <c r="I4" s="1">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1">
+        <v>166</v>
+      </c>
+      <c r="L4" s="1">
+        <v>17</v>
+      </c>
+      <c r="M4" s="1">
+        <v>25</v>
+      </c>
+      <c r="N4" s="1">
+        <v>16</v>
+      </c>
+      <c r="O4" s="1">
+        <v>159</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" si="1"/>
+        <v>478</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="2"/>
+        <v>195</v>
+      </c>
+      <c r="R4" s="1">
+        <f t="shared" si="3"/>
+        <v>211</v>
+      </c>
+      <c r="S4" s="1">
+        <f t="shared" si="4"/>
+        <v>194</v>
+      </c>
+      <c r="T4" s="1">
+        <v>200</v>
+      </c>
+      <c r="U4" s="1">
+        <v>200</v>
+      </c>
+      <c r="V4" s="1">
+        <v>200</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" si="5"/>
+        <v>0.7846153846153846</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" si="6"/>
+        <v>0.78672985781990523</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="7"/>
+        <v>0.81958762886597936</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="8"/>
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" si="9"/>
+        <v>0.83</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" si="10"/>
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" si="12"/>
+        <v>0.79666666666666663</v>
+      </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1279,69 +1470,207 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
+      <c r="G5" s="1">
+        <v>159</v>
+      </c>
+      <c r="H5" s="1">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
+        <v>23</v>
+      </c>
+      <c r="J5" s="1">
+        <v>23</v>
+      </c>
+      <c r="K5" s="1">
+        <v>149</v>
+      </c>
+      <c r="L5" s="1">
+        <v>28</v>
+      </c>
+      <c r="M5" s="1">
+        <v>15</v>
+      </c>
+      <c r="N5" s="1">
+        <v>13</v>
+      </c>
+      <c r="O5" s="1">
+        <v>172</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="2"/>
+        <v>197</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" si="4"/>
+        <v>223</v>
+      </c>
+      <c r="T5" s="1">
+        <v>200</v>
+      </c>
+      <c r="U5" s="1">
+        <v>200</v>
+      </c>
+      <c r="V5" s="1">
+        <v>200</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" si="5"/>
+        <v>0.80710659898477155</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" si="7"/>
+        <v>0.77130044843049328</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="8"/>
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="9"/>
+        <v>0.745</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="10"/>
+        <v>0.86</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="12"/>
+        <v>0.8</v>
+      </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
+      <c r="G6" s="1">
+        <v>154</v>
+      </c>
+      <c r="H6" s="1">
+        <v>23</v>
+      </c>
+      <c r="I6" s="1">
+        <v>23</v>
+      </c>
+      <c r="J6" s="1">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1">
+        <v>153</v>
+      </c>
+      <c r="L6" s="1">
+        <v>30</v>
+      </c>
+      <c r="M6" s="1">
+        <v>14</v>
+      </c>
+      <c r="N6" s="1">
+        <v>8</v>
+      </c>
+      <c r="O6" s="1">
+        <v>178</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="1"/>
+        <v>485</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="3"/>
+        <v>184</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" si="4"/>
+        <v>231</v>
+      </c>
+      <c r="T6" s="1">
+        <v>200</v>
+      </c>
+      <c r="U6" s="1">
+        <v>200</v>
+      </c>
+      <c r="V6" s="1">
+        <v>200</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="5"/>
+        <v>0.83243243243243248</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" si="6"/>
+        <v>0.83152173913043481</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="7"/>
+        <v>0.77056277056277056</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.77</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="9"/>
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="10"/>
+        <v>0.89</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="12"/>
+        <v>0.80833333333333335</v>
+      </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>155</v>
+      </c>
+      <c r="D7" s="1">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1">
+        <v>18</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1369,11 +1698,21 @@
       <c r="AD7" s="1"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1">
+        <v>166</v>
+      </c>
+      <c r="E8" s="1">
+        <v>18</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1401,11 +1740,21 @@
       <c r="AD8" s="1"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1">
+        <v>162</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1466,10 +1815,18 @@
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1497,11 +1854,21 @@
       <c r="AD11" s="1"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1">
+        <v>153</v>
+      </c>
+      <c r="D12" s="1">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1">
+        <v>18</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1529,11 +1896,21 @@
       <c r="AD12" s="1"/>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1">
+        <v>17</v>
+      </c>
+      <c r="D13" s="1">
+        <v>166</v>
+      </c>
+      <c r="E13" s="1">
+        <v>17</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1561,11 +1938,21 @@
       <c r="AD13" s="1"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>25</v>
+      </c>
+      <c r="D14" s="1">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1">
+        <v>159</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1626,10 +2013,18 @@
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1657,11 +2052,21 @@
       <c r="AD16" s="1"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1">
+        <v>159</v>
+      </c>
+      <c r="D17" s="1">
+        <v>18</v>
+      </c>
+      <c r="E17" s="1">
+        <v>23</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1689,11 +2094,21 @@
       <c r="AD17" s="1"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="1">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1">
+        <v>149</v>
+      </c>
+      <c r="E18" s="1">
+        <v>28</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1721,11 +2136,21 @@
       <c r="AD18" s="1"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1">
+        <v>13</v>
+      </c>
+      <c r="E19" s="1">
+        <v>172</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1786,10 +2211,18 @@
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1817,11 +2250,21 @@
       <c r="AD21" s="1"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="1">
+        <v>154</v>
+      </c>
+      <c r="D22" s="1">
+        <v>23</v>
+      </c>
+      <c r="E22" s="1">
+        <v>23</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1849,11 +2292,21 @@
       <c r="AD22" s="1"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1">
+        <v>153</v>
+      </c>
+      <c r="E23" s="1">
+        <v>30</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1881,11 +2334,21 @@
       <c r="AD23" s="1"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="1">
+        <v>14</v>
+      </c>
+      <c r="D24" s="1">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1">
+        <v>178</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
